--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/INDIANA_2022.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2022/INDIANA_2022.xlsx
@@ -4632,7 +4632,7 @@
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C238">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B247" t="inlineStr">
         <is>
-          <t>Dolores Hidalgo Cuna De La Independencia Nacional</t>
+          <t>Dolores Hidalgo</t>
         </is>
       </c>
       <c r="C247">
@@ -12595,7 +12595,7 @@
         <v>97</v>
       </c>
       <c r="D680">
-        <v>0.009766411598872331</v>
+        <v>0.009766411598872333</v>
       </c>
     </row>
     <row r="681">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="B685" t="inlineStr">
         <is>
-          <t>San Juan Mixtepec - Distr. 08 -</t>
+          <t>San Juan Mixtepec -Dto. 08 -</t>
         </is>
       </c>
       <c r="C685">
@@ -13092,7 +13092,7 @@
       </c>
       <c r="B708" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C708">
@@ -14172,7 +14172,7 @@
       </c>
       <c r="B768" t="inlineStr">
         <is>
-          <t>Santo Domingo Tonaltepec</t>
+          <t>Santo Domingo Tomaltepec</t>
         </is>
       </c>
       <c r="C768">
@@ -15241,7 +15241,7 @@
         <v>91</v>
       </c>
       <c r="D827">
-        <v>0.009162303664921465</v>
+        <v>0.009162303664921463</v>
       </c>
     </row>
     <row r="828">
